--- a/資料庫分類.xlsx
+++ b/資料庫分類.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
   <si>
     <t>評論系統資料庫</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -118,57 +118,173 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>使用者名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>電子信箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>密碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生日</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>註冊日期</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>身分組</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>users</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>birthdate</t>
+  </si>
+  <si>
+    <t>join_date</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>SDGS分類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>slug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>created_at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>image_path</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>categories</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分類名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">分類的 URL </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分類描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立時間</t>
+  </si>
+  <si>
+    <t>建立時間</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖片檔案路徑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檢舉文章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>user_id</t>
+  </si>
+  <si>
+    <t>user_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reported_at</t>
+  </si>
+  <si>
+    <t>report_message</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>檢舉留言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment_id</t>
+  </si>
+  <si>
     <t>編號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用者名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>電子信箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>密碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生日</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>註冊日期</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>身分組</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>users</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>birthdate</t>
-  </si>
-  <si>
-    <t>join_date</t>
-  </si>
-  <si>
-    <t>bio</t>
-  </si>
-  <si>
-    <t>role</t>
+  </si>
+  <si>
+    <t>編號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文章 ID</t>
+  </si>
+  <si>
+    <t>使用者 ID</t>
+  </si>
+  <si>
+    <t>檢舉的具體時間</t>
+  </si>
+  <si>
+    <t>檢舉時的附加訊息</t>
+  </si>
+  <si>
+    <t>檢舉時的附加訊息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>檢舉的處理狀態</t>
+  </si>
+  <si>
+    <t>留言 ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>report_commet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>post_reports</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -503,15 +619,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
@@ -622,59 +738,210 @@
         <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>